--- a/students/leetcode_Links.xlsx
+++ b/students/leetcode_Links.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KALAI\Documents\Leetcode-Automation\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9345883E-0DD2-4A57-BF6D-60B900FDF1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863190D4-5FC7-4920-B8A5-A0BC9A2BB47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A1D85D54-F45A-40AC-9A85-717C16392CF8}"/>
+    <workbookView xWindow="0" yWindow="1572" windowWidth="23040" windowHeight="11388" xr2:uid="{A1D85D54-F45A-40AC-9A85-717C16392CF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="146">
   <si>
     <t>S.No</t>
   </si>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>https://leetcode.com/u/thiruselvan_2005/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/u/HRamamoorthy/</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1525,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -1556,7 +1559,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -1671,7 +1674,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -1752,9 +1755,11 @@
       <c r="D44" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E44" s="10"/>
-    </row>
-    <row r="45" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E44" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -1771,7 +1776,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -1887,6 +1892,7 @@
     <hyperlink ref="E26" r:id="rId10" xr:uid="{E3B68B0F-4454-4835-A5D0-AAC4BF11A8EA}"/>
     <hyperlink ref="E43" r:id="rId11" xr:uid="{6043E885-2163-4621-B2B5-5550BBEEB7EF}"/>
     <hyperlink ref="E49" r:id="rId12" xr:uid="{8864BC88-DF7F-4023-8D92-062CE90DB5A0}"/>
+    <hyperlink ref="E44" r:id="rId13" xr:uid="{F46EEA24-0D18-4E74-BDE9-4051C32DF5EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students/leetcode_Links.xlsx
+++ b/students/leetcode_Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KALAI\Documents\Leetcode-Automation\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863190D4-5FC7-4920-B8A5-A0BC9A2BB47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53781062-DB08-455C-9ADA-FE211AE56839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1572" windowWidth="23040" windowHeight="11388" xr2:uid="{A1D85D54-F45A-40AC-9A85-717C16392CF8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
   <si>
     <t>S.No</t>
   </si>
@@ -477,6 +477,12 @@
   </si>
   <si>
     <t>https://leetcode.com/u/HRamamoorthy/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/u/IroXEV3ekA/</t>
+  </si>
+  <si>
+    <t>IroXEV3ekA</t>
   </si>
 </sst>
 </file>
@@ -1586,8 +1592,12 @@
       <c r="C34" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10"/>
+      <c r="D34" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
@@ -1893,6 +1903,7 @@
     <hyperlink ref="E43" r:id="rId11" xr:uid="{6043E885-2163-4621-B2B5-5550BBEEB7EF}"/>
     <hyperlink ref="E49" r:id="rId12" xr:uid="{8864BC88-DF7F-4023-8D92-062CE90DB5A0}"/>
     <hyperlink ref="E44" r:id="rId13" xr:uid="{F46EEA24-0D18-4E74-BDE9-4051C32DF5EF}"/>
+    <hyperlink ref="E34" r:id="rId14" xr:uid="{8C4C6B10-6941-4F8D-B442-F51E39EC1135}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
